--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2023_atacama.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2023_atacama.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -417,7 +417,7 @@
         <v>15.52132600567722</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -444,7 +444,7 @@
         <v>12.33981513152547</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -471,13 +471,13 @@
         <v>13.5027682483138</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Chañaral</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -486,25 +486,25 @@
         </is>
       </c>
       <c r="C5">
-        <v>309431.66</v>
+        <v>324411.47</v>
       </c>
       <c r="D5">
-        <v>275149</v>
+        <v>285314.69</v>
       </c>
       <c r="E5">
-        <v>34282.65999999997</v>
+        <v>39096.77999999997</v>
       </c>
       <c r="F5">
-        <v>12.45967094192599</v>
+        <v>13.7030378632099</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Chañaral</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -513,25 +513,25 @@
         </is>
       </c>
       <c r="C6">
-        <v>734112.9399999999</v>
+        <v>684929.6899999999</v>
       </c>
       <c r="D6">
-        <v>671582.12</v>
+        <v>622193.3100000001</v>
       </c>
       <c r="E6">
-        <v>62530.81999999995</v>
+        <v>62736.37999999989</v>
       </c>
       <c r="F6">
-        <v>9.310971530927592</v>
+        <v>10.08310102209229</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chañaral</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -540,25 +540,25 @@
         </is>
       </c>
       <c r="C7">
-        <v>530344.9399999999</v>
+        <v>508569.41</v>
       </c>
       <c r="D7">
-        <v>480115.28</v>
+        <v>456918.44</v>
       </c>
       <c r="E7">
-        <v>50229.65999999992</v>
+        <v>51650.96999999997</v>
       </c>
       <c r="F7">
-        <v>10.461999876363</v>
+        <v>11.3041990601211</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Chañaral</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -567,25 +567,25 @@
         </is>
       </c>
       <c r="C8">
-        <v>348075.12</v>
+        <v>309431.66</v>
       </c>
       <c r="D8">
-        <v>307155.94</v>
+        <v>275149</v>
       </c>
       <c r="E8">
-        <v>40919.17999999999</v>
+        <v>34282.65999999997</v>
       </c>
       <c r="F8">
-        <v>13.32195626755581</v>
+        <v>12.45967094192599</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Chañaral</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -594,45 +594,126 @@
         </is>
       </c>
       <c r="C9">
-        <v>705488</v>
+        <v>734112.9399999999</v>
       </c>
       <c r="D9">
-        <v>644438.88</v>
+        <v>671582.12</v>
       </c>
       <c r="E9">
-        <v>61049.12</v>
+        <v>62530.81999999995</v>
       </c>
       <c r="F9">
-        <v>9.47322110670914</v>
+        <v>9.310971530927592</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>530344.9399999999</v>
+      </c>
+      <c r="D10">
+        <v>480115.28</v>
+      </c>
+      <c r="E10">
+        <v>50229.65999999992</v>
+      </c>
+      <c r="F10">
+        <v>10.461999876363</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Copiapó</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>348075.12</v>
+      </c>
+      <c r="D11">
+        <v>307155.94</v>
+      </c>
+      <c r="E11">
+        <v>40919.17999999999</v>
+      </c>
+      <c r="F11">
+        <v>13.32195626755581</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>705488</v>
+      </c>
+      <c r="D12">
+        <v>644438.88</v>
+      </c>
+      <c r="E12">
+        <v>61049.12</v>
+      </c>
+      <c r="F12">
+        <v>9.47322110670914</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C10">
+      <c r="C13">
         <v>530412.3100000001</v>
       </c>
-      <c r="D10">
+      <c r="D13">
         <v>478981.03</v>
       </c>
-      <c r="E10">
+      <c r="E13">
         <v>51431.28000000003</v>
       </c>
-      <c r="F10">
+      <c r="F13">
         <v>10.73764445326781</v>
       </c>
-      <c r="G10">
+      <c r="G13">
         <v>1</v>
       </c>
     </row>
@@ -695,7 +776,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -882,6 +963,60 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>456918.44</v>
+      </c>
+      <c r="D11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>508569.41</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>520234.53</v>
+      </c>
+      <c r="D13" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2023_atacama.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2023_atacama.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t xml:space="preserve">Provincia</t>
   </si>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:09</t>
+    <t xml:space="preserve">2026-08-19 14:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -83,13 +83,19 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">prov_i_ingr_mean_a_2023_atacama.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingreso de la población en edad de trabajar</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region de Atacama</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
@@ -833,23 +839,23 @@
         <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -872,7 +878,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2">
@@ -921,10 +927,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
@@ -932,7 +938,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>480115.28</v>
@@ -943,7 +949,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>530344.94</v>
@@ -954,7 +960,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>536926.5</v>
@@ -965,7 +971,7 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>478981.03</v>
@@ -976,7 +982,7 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>530412.31</v>
@@ -987,7 +993,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>543795.88</v>
@@ -998,7 +1004,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>394778.53</v>
@@ -1009,7 +1015,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>448084.56</v>
@@ -1020,7 +1026,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>457152.03</v>
@@ -1031,7 +1037,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>456918.44</v>
@@ -1042,7 +1048,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>508569.41</v>
@@ -1053,7 +1059,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>520234.53</v>

--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2023_atacama.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2023_atacama.xlsx
@@ -71,7 +71,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 14:24</t>
+    <t xml:space="preserve">2026-09-07 11:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
